--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_as_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_as_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>14-09-2021 08:30</t>
+          <t>2021-09-14 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="inlineStr"/>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="inlineStr"/>
@@ -4273,7 +4273,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="inlineStr"/>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6450,7 +6450,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -6925,7 +6925,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>20-12-2021 08:30</t>
+          <t>2021-12-20 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>09-07-2021 08:30</t>
+          <t>2021-09-07 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8255,7 +8255,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8825,7 +8825,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9015,7 +9015,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>14-09-2021 08:30</t>
+          <t>2021-09-14 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9490,7 +9490,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10244,7 +10244,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10434,7 +10434,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>27-07-2021 08:30</t>
+          <t>2021-07-27 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12138,7 +12138,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12324,7 +12324,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12603,7 +12603,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12882,7 +12882,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -12975,7 +12975,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13254,7 +13254,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13347,7 +13347,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="inlineStr"/>
@@ -13440,7 +13440,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr"/>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13626,7 +13626,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -13719,7 +13719,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr"/>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -13998,7 +13998,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr"/>
@@ -14091,7 +14091,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr"/>
@@ -14277,7 +14277,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14370,7 +14370,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr"/>
@@ -14463,7 +14463,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="inlineStr"/>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="inlineStr"/>
@@ -14742,7 +14742,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr"/>
@@ -14835,7 +14835,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -14928,7 +14928,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr"/>
@@ -15021,7 +15021,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15486,7 +15486,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15579,7 +15579,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15672,7 +15672,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -15765,7 +15765,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -15951,7 +15951,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="inlineStr"/>
@@ -16044,7 +16044,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16139,7 +16139,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16234,7 +16234,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -16804,7 +16804,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -16899,7 +16899,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>27-12-2021 08:30</t>
+          <t>2021-12-27 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17184,7 +17184,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17279,7 +17279,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17469,7 +17469,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -17564,7 +17564,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -17754,7 +17754,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -17944,7 +17944,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18039,7 +18039,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18134,7 +18134,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18514,7 +18514,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -18799,7 +18799,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -18894,7 +18894,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="n">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="n">
@@ -19084,7 +19084,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="n">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19369,7 +19369,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19559,7 +19559,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -19749,7 +19749,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="n">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -20127,7 +20127,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20220,7 +20220,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20313,7 +20313,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20406,7 +20406,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -20592,7 +20592,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -20778,7 +20778,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -20871,7 +20871,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -20964,7 +20964,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21057,7 +21057,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21150,7 +21150,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21243,7 +21243,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21336,7 +21336,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21429,7 +21429,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21522,7 +21522,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -21615,7 +21615,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -21708,7 +21708,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -21801,7 +21801,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -21894,7 +21894,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
@@ -21987,7 +21987,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
@@ -22080,7 +22080,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -22173,7 +22173,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
@@ -22266,7 +22266,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22359,7 +22359,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22452,7 +22452,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22545,7 +22545,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="n">
@@ -22640,7 +22640,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="n">
@@ -22735,7 +22735,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="n">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="n">
@@ -22925,7 +22925,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="n">
@@ -23020,7 +23020,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="n">
@@ -23115,7 +23115,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="n">
@@ -23210,7 +23210,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23305,7 +23305,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23400,7 +23400,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23495,7 +23495,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23588,7 +23588,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -23681,7 +23681,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -23774,7 +23774,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr"/>
@@ -23867,7 +23867,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr"/>
@@ -23960,7 +23960,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24053,7 +24053,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24146,7 +24146,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24239,7 +24239,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr"/>
@@ -24332,7 +24332,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24522,7 +24522,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -24617,7 +24617,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -24712,7 +24712,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -24807,7 +24807,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -24902,7 +24902,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25092,7 +25092,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
@@ -25187,7 +25187,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="n">
@@ -25282,7 +25282,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="inlineStr"/>
@@ -25375,7 +25375,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="inlineStr"/>
@@ -25468,7 +25468,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="inlineStr"/>
@@ -25561,7 +25561,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="inlineStr"/>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="inlineStr"/>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="inlineStr"/>
@@ -25840,7 +25840,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="inlineStr"/>
@@ -25933,7 +25933,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26026,7 +26026,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -26119,7 +26119,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="inlineStr"/>
@@ -26212,7 +26212,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="inlineStr"/>
@@ -26305,7 +26305,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="inlineStr"/>
@@ -26398,7 +26398,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="inlineStr"/>
@@ -26491,7 +26491,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="inlineStr"/>
@@ -26584,7 +26584,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="inlineStr"/>
@@ -26677,7 +26677,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="n">
@@ -26772,7 +26772,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="n">
@@ -26867,7 +26867,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="n">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="n">
@@ -27057,7 +27057,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="n">
@@ -27152,7 +27152,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="n">
@@ -27247,7 +27247,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="n">
@@ -27342,7 +27342,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="n">
@@ -27437,7 +27437,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="n">
@@ -27532,7 +27532,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="inlineStr"/>
@@ -27625,7 +27625,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="inlineStr"/>
@@ -27718,7 +27718,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="inlineStr"/>
@@ -27811,7 +27811,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="inlineStr"/>
@@ -27904,7 +27904,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="inlineStr"/>
@@ -27997,7 +27997,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="inlineStr"/>
@@ -28090,7 +28090,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="n">
@@ -28185,7 +28185,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="n">
@@ -28280,7 +28280,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="n">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="n">
@@ -28470,7 +28470,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="n">
@@ -28565,7 +28565,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="n">
@@ -28660,7 +28660,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="n">
@@ -28850,7 +28850,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="n">
@@ -28945,7 +28945,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="n">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="n">
@@ -29135,7 +29135,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29230,7 +29230,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="n">
@@ -29325,7 +29325,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -29420,7 +29420,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="n">
@@ -29610,7 +29610,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="n">
@@ -29705,7 +29705,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="n">
@@ -29800,7 +29800,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="n">
@@ -29895,7 +29895,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="n">
@@ -29990,7 +29990,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="n">
@@ -30085,7 +30085,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="n">
@@ -30180,7 +30180,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="n">
@@ -30275,7 +30275,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="n">
@@ -30370,7 +30370,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="n">
@@ -30465,7 +30465,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="n">
@@ -30560,7 +30560,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="n">
@@ -30655,7 +30655,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="n">
@@ -30750,7 +30750,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="n">
@@ -30845,7 +30845,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="n">
@@ -30940,7 +30940,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="n">
@@ -31035,7 +31035,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="n">
@@ -31130,7 +31130,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="n">
@@ -31225,7 +31225,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="n">
@@ -31320,7 +31320,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="n">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>09-05-2021 08:30</t>
+          <t>2021-09-05 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="n">
@@ -31510,7 +31510,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="n">
@@ -31605,7 +31605,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="n">
@@ -31700,7 +31700,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="n">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="n">
@@ -31890,7 +31890,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="n">
@@ -31985,7 +31985,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="n">
@@ -32080,7 +32080,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="n">
@@ -32175,7 +32175,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="n">
@@ -32270,7 +32270,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="n">
@@ -32365,7 +32365,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="n">
@@ -32460,7 +32460,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="n">
@@ -32555,7 +32555,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="n">
@@ -32650,7 +32650,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="n">
@@ -32745,7 +32745,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="n">
@@ -32840,7 +32840,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="n">
@@ -32935,7 +32935,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="n">
@@ -33030,7 +33030,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="n">
@@ -33125,7 +33125,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>29-04-2021 08:30</t>
+          <t>2021-04-29 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="n">
@@ -33226,7 +33226,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="n">
@@ -33327,7 +33327,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="n">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="n">
@@ -33529,7 +33529,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="n">
@@ -33630,7 +33630,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="n">
@@ -33731,7 +33731,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="n">
@@ -33832,7 +33832,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="n">
@@ -33933,7 +33933,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34135,7 +34135,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34236,7 +34236,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34337,7 +34337,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="n">
@@ -34438,7 +34438,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -34539,7 +34539,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -34640,7 +34640,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -34741,7 +34741,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -34842,7 +34842,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="n">
@@ -34943,7 +34943,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>09-07-2021 08:30</t>
+          <t>2021-09-07 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="n">
@@ -35044,7 +35044,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="n">
@@ -35145,7 +35145,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="n">
@@ -35246,7 +35246,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="n">
@@ -35347,7 +35347,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>29-04-2021 08:30</t>
+          <t>2021-04-29 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="n">
@@ -35448,7 +35448,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="n">
@@ -35549,7 +35549,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="n">
@@ -35650,7 +35650,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="n">
@@ -35751,7 +35751,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="n">
@@ -35852,7 +35852,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="n">
@@ -35953,7 +35953,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="n">
@@ -36054,7 +36054,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="n">
@@ -36155,7 +36155,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="n">
@@ -36256,7 +36256,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="n">
@@ -36357,7 +36357,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="n">
@@ -36458,7 +36458,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="n">
@@ -36559,7 +36559,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="n">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="n">
@@ -36761,7 +36761,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="n">
@@ -36862,7 +36862,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="n">
@@ -36963,7 +36963,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="n">
@@ -37064,7 +37064,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="n">
@@ -37165,7 +37165,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="n">
@@ -37266,7 +37266,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="n">
@@ -37367,7 +37367,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="n">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="n">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="n">
@@ -37670,7 +37670,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -37771,7 +37771,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -37872,7 +37872,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="n">
@@ -37973,7 +37973,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="n">
@@ -38074,7 +38074,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="n">
@@ -38175,7 +38175,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="n">
@@ -38276,7 +38276,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="n">
@@ -38377,7 +38377,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="n">
@@ -38478,7 +38478,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="n">
@@ -38579,7 +38579,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="n">
@@ -38680,7 +38680,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="n">
@@ -38781,7 +38781,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>25-11-2021 08:30</t>
+          <t>2021-11-25 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="n">
@@ -38882,7 +38882,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="n">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="n">
@@ -39084,7 +39084,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="n">
@@ -39185,7 +39185,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="n">
@@ -39286,7 +39286,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="n">
@@ -39387,7 +39387,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="n">
@@ -39488,7 +39488,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="n">
@@ -39589,7 +39589,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="n">
@@ -39690,7 +39690,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="n">
@@ -39791,7 +39791,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>27-07-2021 08:30</t>
+          <t>2021-07-27 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="n">
@@ -39892,7 +39892,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="n">
@@ -39993,7 +39993,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="n">
@@ -40094,7 +40094,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="n">
@@ -40195,7 +40195,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="n">
@@ -40296,7 +40296,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="n">
@@ -40397,7 +40397,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="n">
@@ -40498,7 +40498,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="n">
@@ -40599,7 +40599,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="n">
@@ -40700,7 +40700,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="n">
@@ -40801,7 +40801,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="n">
@@ -40902,7 +40902,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="n">
@@ -41003,7 +41003,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="n">
@@ -41104,7 +41104,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="n">
@@ -41205,7 +41205,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="n">
@@ -41306,7 +41306,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>22-07-2021 08:30</t>
+          <t>2021-07-22 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="n">
@@ -41407,7 +41407,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="n">
@@ -41508,7 +41508,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="n">
@@ -41609,7 +41609,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="n">
@@ -41710,7 +41710,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>09-05-2021 08:30</t>
+          <t>2021-09-05 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="n">
@@ -41811,7 +41811,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="n">
@@ -41912,7 +41912,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>09-05-2021 08:30</t>
+          <t>2021-09-05 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="n">
@@ -42013,7 +42013,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="n">
@@ -42114,7 +42114,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="n">
@@ -42215,7 +42215,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="n">
@@ -42316,7 +42316,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="n">
@@ -42417,7 +42417,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="n">
@@ -42518,7 +42518,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="n">
@@ -42619,7 +42619,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="n">
@@ -42720,7 +42720,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="n">
@@ -42821,7 +42821,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="n">
@@ -42922,7 +42922,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="n">
@@ -43023,7 +43023,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="n">
@@ -43124,7 +43124,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="n">
@@ -43225,7 +43225,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="n">
@@ -43326,7 +43326,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="n">
@@ -43427,7 +43427,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="n">
@@ -43528,7 +43528,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="n">
@@ -43629,7 +43629,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>09-05-2021 08:30</t>
+          <t>2021-09-05 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="n">
@@ -43730,7 +43730,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="n">
@@ -43831,7 +43831,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="n">
@@ -43932,7 +43932,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="n">
@@ -44033,7 +44033,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="n">
@@ -44128,7 +44128,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="n">
@@ -44223,7 +44223,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="n">
@@ -44318,7 +44318,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="n">
@@ -44413,7 +44413,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="n">
@@ -44508,7 +44508,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="n">
@@ -44603,7 +44603,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="n">
@@ -44698,7 +44698,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="n">
@@ -44793,7 +44793,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="n">
@@ -44888,7 +44888,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>20-12-2021 08:30</t>
+          <t>2021-12-20 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="n">
@@ -44983,7 +44983,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="n">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="n">
@@ -45173,7 +45173,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="n">
@@ -45268,7 +45268,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="n">
@@ -45363,7 +45363,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>09-07-2021 08:30</t>
+          <t>2021-09-07 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="n">
@@ -45458,7 +45458,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="n">
@@ -45553,7 +45553,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="n">
@@ -45648,7 +45648,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="n">
@@ -45743,7 +45743,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="n">
@@ -45838,7 +45838,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="n">
@@ -45933,7 +45933,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="n">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="inlineStr"/>
@@ -46127,7 +46127,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="inlineStr"/>
@@ -46220,7 +46220,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="inlineStr"/>
@@ -46313,7 +46313,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="n">
@@ -46408,7 +46408,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="n">
@@ -46503,7 +46503,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="n">
@@ -46598,7 +46598,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>28-04-2021 08:30</t>
+          <t>2021-04-28 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="n">
@@ -46693,7 +46693,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="n">
@@ -46788,7 +46788,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>22-09-2021 08:30</t>
+          <t>2021-09-22 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="n">
@@ -46883,7 +46883,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="n">
@@ -46978,7 +46978,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>23-11-2021 08:30</t>
+          <t>2021-11-23 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="n">
@@ -47073,7 +47073,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>21-12-2021 08:30</t>
+          <t>2021-12-21 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="n">
@@ -47168,7 +47168,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="inlineStr"/>
@@ -47261,7 +47261,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="inlineStr"/>
@@ -47354,7 +47354,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="inlineStr"/>
@@ -47447,7 +47447,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="inlineStr"/>
@@ -47540,7 +47540,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="inlineStr"/>
@@ -47633,7 +47633,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="inlineStr"/>
@@ -47726,7 +47726,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="n">
@@ -47821,7 +47821,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="n">
@@ -47916,7 +47916,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="n">
@@ -48011,7 +48011,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="n">
@@ -48106,7 +48106,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="n">
@@ -48201,7 +48201,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="n">
@@ -48296,7 +48296,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="n">
@@ -48391,7 +48391,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="n">
@@ -48486,7 +48486,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="n">
@@ -48581,7 +48581,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="n">
@@ -48676,7 +48676,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="inlineStr"/>
@@ -48769,7 +48769,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="inlineStr"/>
@@ -48862,7 +48862,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="inlineStr"/>
@@ -48955,7 +48955,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="n">
@@ -49050,7 +49050,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="n">
@@ -49145,7 +49145,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="n">
@@ -49240,7 +49240,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="n">
@@ -49335,7 +49335,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="n">
@@ -49430,7 +49430,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="n">
@@ -49525,7 +49525,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>14-09-2021 08:30</t>
+          <t>2021-09-14 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="n">
@@ -49620,7 +49620,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>20-10-2021 08:30</t>
+          <t>2021-10-20 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="n">
@@ -49715,7 +49715,7 @@
       </c>
       <c r="S515" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T515" t="n">
@@ -49810,7 +49810,7 @@
       </c>
       <c r="S516" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T516" t="n">
@@ -49905,7 +49905,7 @@
       </c>
       <c r="S517" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T517" t="n">
@@ -50000,7 +50000,7 @@
       </c>
       <c r="S518" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T518" t="n">
@@ -50095,7 +50095,7 @@
       </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T519" t="n">
@@ -50190,7 +50190,7 @@
       </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T520" t="n">
@@ -50285,7 +50285,7 @@
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T521" t="n">
@@ -50380,7 +50380,7 @@
       </c>
       <c r="S522" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T522" t="n">
@@ -50475,7 +50475,7 @@
       </c>
       <c r="S523" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T523" t="n">
@@ -50570,7 +50570,7 @@
       </c>
       <c r="S524" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T524" t="n">
@@ -50665,7 +50665,7 @@
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T525" t="n">
@@ -50760,7 +50760,7 @@
       </c>
       <c r="S526" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T526" t="n">
@@ -50855,7 +50855,7 @@
       </c>
       <c r="S527" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T527" t="inlineStr"/>
@@ -50948,7 +50948,7 @@
       </c>
       <c r="S528" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T528" t="inlineStr"/>
@@ -51041,7 +51041,7 @@
       </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T529" t="inlineStr"/>
@@ -51134,7 +51134,7 @@
       </c>
       <c r="S530" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T530" t="inlineStr"/>
@@ -51227,7 +51227,7 @@
       </c>
       <c r="S531" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T531" t="inlineStr"/>
@@ -51320,7 +51320,7 @@
       </c>
       <c r="S532" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T532" t="inlineStr"/>
@@ -51413,7 +51413,7 @@
       </c>
       <c r="S533" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T533" t="inlineStr"/>
@@ -51506,7 +51506,7 @@
       </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T534" t="inlineStr"/>
@@ -51599,7 +51599,7 @@
       </c>
       <c r="S535" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T535" t="inlineStr"/>
@@ -51692,7 +51692,7 @@
       </c>
       <c r="S536" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T536" t="inlineStr"/>
@@ -51785,7 +51785,7 @@
       </c>
       <c r="S537" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T537" t="inlineStr"/>
@@ -51878,7 +51878,7 @@
       </c>
       <c r="S538" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T538" t="inlineStr"/>
@@ -51971,7 +51971,7 @@
       </c>
       <c r="S539" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T539" t="inlineStr"/>
@@ -52064,7 +52064,7 @@
       </c>
       <c r="S540" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T540" t="inlineStr"/>
@@ -52157,7 +52157,7 @@
       </c>
       <c r="S541" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T541" t="inlineStr"/>
@@ -52250,7 +52250,7 @@
       </c>
       <c r="S542" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T542" t="inlineStr"/>
@@ -52343,7 +52343,7 @@
       </c>
       <c r="S543" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T543" t="inlineStr"/>
@@ -52436,7 +52436,7 @@
       </c>
       <c r="S544" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T544" t="inlineStr"/>
@@ -52529,7 +52529,7 @@
       </c>
       <c r="S545" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T545" t="inlineStr"/>
@@ -52622,7 +52622,7 @@
       </c>
       <c r="S546" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T546" t="inlineStr"/>
@@ -52715,7 +52715,7 @@
       </c>
       <c r="S547" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T547" t="inlineStr"/>
@@ -52808,7 +52808,7 @@
       </c>
       <c r="S548" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T548" t="inlineStr"/>
@@ -52901,7 +52901,7 @@
       </c>
       <c r="S549" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T549" t="inlineStr"/>
@@ -52994,7 +52994,7 @@
       </c>
       <c r="S550" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T550" t="inlineStr"/>
@@ -53087,7 +53087,7 @@
       </c>
       <c r="S551" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T551" t="inlineStr"/>
@@ -53180,7 +53180,7 @@
       </c>
       <c r="S552" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T552" t="inlineStr"/>
@@ -53273,7 +53273,7 @@
       </c>
       <c r="S553" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T553" t="inlineStr"/>
@@ -53366,7 +53366,7 @@
       </c>
       <c r="S554" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T554" t="inlineStr"/>
@@ -53459,7 +53459,7 @@
       </c>
       <c r="S555" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T555" t="inlineStr"/>
@@ -53552,7 +53552,7 @@
       </c>
       <c r="S556" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T556" t="inlineStr"/>
@@ -53645,7 +53645,7 @@
       </c>
       <c r="S557" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T557" t="inlineStr"/>
@@ -53738,7 +53738,7 @@
       </c>
       <c r="S558" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T558" t="inlineStr"/>
@@ -53831,7 +53831,7 @@
       </c>
       <c r="S559" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T559" t="inlineStr"/>
@@ -53924,7 +53924,7 @@
       </c>
       <c r="S560" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T560" t="inlineStr"/>
@@ -54017,7 +54017,7 @@
       </c>
       <c r="S561" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T561" t="inlineStr"/>
@@ -54110,7 +54110,7 @@
       </c>
       <c r="S562" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T562" t="inlineStr"/>
@@ -54203,7 +54203,7 @@
       </c>
       <c r="S563" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T563" t="inlineStr"/>
@@ -54296,7 +54296,7 @@
       </c>
       <c r="S564" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T564" t="inlineStr"/>
@@ -54389,7 +54389,7 @@
       </c>
       <c r="S565" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T565" t="inlineStr"/>
@@ -54482,7 +54482,7 @@
       </c>
       <c r="S566" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T566" t="inlineStr"/>
@@ -54575,7 +54575,7 @@
       </c>
       <c r="S567" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T567" t="inlineStr"/>
@@ -54668,7 +54668,7 @@
       </c>
       <c r="S568" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T568" t="inlineStr"/>
@@ -54761,7 +54761,7 @@
       </c>
       <c r="S569" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T569" t="n">
@@ -54856,7 +54856,7 @@
       </c>
       <c r="S570" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T570" t="n">
@@ -54951,7 +54951,7 @@
       </c>
       <c r="S571" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T571" t="n">
@@ -55046,7 +55046,7 @@
       </c>
       <c r="S572" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T572" t="n">
@@ -55141,7 +55141,7 @@
       </c>
       <c r="S573" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T573" t="n">
@@ -55236,7 +55236,7 @@
       </c>
       <c r="S574" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T574" t="n">
@@ -55331,7 +55331,7 @@
       </c>
       <c r="S575" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T575" t="n">
@@ -55426,7 +55426,7 @@
       </c>
       <c r="S576" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T576" t="n">
@@ -55521,7 +55521,7 @@
       </c>
       <c r="S577" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T577" t="n">
@@ -55616,7 +55616,7 @@
       </c>
       <c r="S578" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T578" t="n">
@@ -55711,7 +55711,7 @@
       </c>
       <c r="S579" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T579" t="n">
@@ -55806,7 +55806,7 @@
       </c>
       <c r="S580" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T580" t="n">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="S581" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T581" t="n">
@@ -55996,7 +55996,7 @@
       </c>
       <c r="S582" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T582" t="n">
@@ -56091,7 +56091,7 @@
       </c>
       <c r="S583" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T583" t="n">
@@ -56186,7 +56186,7 @@
       </c>
       <c r="S584" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T584" t="n">
@@ -56281,7 +56281,7 @@
       </c>
       <c r="S585" t="inlineStr">
         <is>
-          <t>14-09-2021 08:30</t>
+          <t>2021-09-14 08:30:00</t>
         </is>
       </c>
       <c r="T585" t="n">
@@ -56376,7 +56376,7 @@
       </c>
       <c r="S586" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T586" t="n">
@@ -56471,7 +56471,7 @@
       </c>
       <c r="S587" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T587" t="n">
@@ -56566,7 +56566,7 @@
       </c>
       <c r="S588" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T588" t="n">
@@ -56661,7 +56661,7 @@
       </c>
       <c r="S589" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T589" t="inlineStr"/>
@@ -56754,7 +56754,7 @@
       </c>
       <c r="S590" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T590" t="inlineStr"/>
@@ -56847,7 +56847,7 @@
       </c>
       <c r="S591" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T591" t="inlineStr"/>
@@ -56940,7 +56940,7 @@
       </c>
       <c r="S592" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T592" t="inlineStr"/>
@@ -57033,7 +57033,7 @@
       </c>
       <c r="S593" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T593" t="inlineStr"/>
@@ -57126,7 +57126,7 @@
       </c>
       <c r="S594" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T594" t="inlineStr"/>
@@ -57219,7 +57219,7 @@
       </c>
       <c r="S595" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T595" t="n">
@@ -57314,7 +57314,7 @@
       </c>
       <c r="S596" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T596" t="n">
@@ -57409,7 +57409,7 @@
       </c>
       <c r="S597" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T597" t="n">
@@ -57504,7 +57504,7 @@
       </c>
       <c r="S598" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T598" t="n">
@@ -57599,7 +57599,7 @@
       </c>
       <c r="S599" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T599" t="n">
@@ -57694,7 +57694,7 @@
       </c>
       <c r="S600" t="inlineStr">
         <is>
-          <t>18-08-2021 08:30</t>
+          <t>2021-08-18 08:30:00</t>
         </is>
       </c>
       <c r="T600" t="n">
@@ -57789,7 +57789,7 @@
       </c>
       <c r="S601" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T601" t="n">
@@ -57884,7 +57884,7 @@
       </c>
       <c r="S602" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T602" t="n">
@@ -57979,7 +57979,7 @@
       </c>
       <c r="S603" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T603" t="n">
@@ -58074,7 +58074,7 @@
       </c>
       <c r="S604" t="inlineStr">
         <is>
-          <t>20-12-2021 08:30</t>
+          <t>2021-12-20 08:30:00</t>
         </is>
       </c>
       <c r="T604" t="n">
@@ -58169,7 +58169,7 @@
       </c>
       <c r="S605" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T605" t="inlineStr"/>
@@ -58262,7 +58262,7 @@
       </c>
       <c r="S606" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T606" t="inlineStr"/>
@@ -58355,7 +58355,7 @@
       </c>
       <c r="S607" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T607" t="inlineStr"/>
@@ -58448,7 +58448,7 @@
       </c>
       <c r="S608" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T608" t="n">
@@ -58543,7 +58543,7 @@
       </c>
       <c r="S609" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T609" t="n">
@@ -58638,7 +58638,7 @@
       </c>
       <c r="S610" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T610" t="n">
@@ -58733,7 +58733,7 @@
       </c>
       <c r="S611" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T611" t="n">
@@ -58828,7 +58828,7 @@
       </c>
       <c r="S612" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T612" t="n">
@@ -58923,7 +58923,7 @@
       </c>
       <c r="S613" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T613" t="n">
@@ -59018,7 +59018,7 @@
       </c>
       <c r="S614" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T614" t="n">
@@ -59113,7 +59113,7 @@
       </c>
       <c r="S615" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T615" t="n">
@@ -59208,7 +59208,7 @@
       </c>
       <c r="S616" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T616" t="n">
@@ -59303,7 +59303,7 @@
       </c>
       <c r="S617" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T617" t="n">
@@ -59398,7 +59398,7 @@
       </c>
       <c r="S618" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T618" t="n">
@@ -59493,7 +59493,7 @@
       </c>
       <c r="S619" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T619" t="inlineStr"/>
@@ -59586,7 +59586,7 @@
       </c>
       <c r="S620" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T620" t="inlineStr"/>
@@ -59679,7 +59679,7 @@
       </c>
       <c r="S621" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T621" t="inlineStr"/>
@@ -59772,7 +59772,7 @@
       </c>
       <c r="S622" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T622" t="n">
@@ -59867,7 +59867,7 @@
       </c>
       <c r="S623" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T623" t="n">
@@ -59962,7 +59962,7 @@
       </c>
       <c r="S624" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T624" t="n">
@@ -60057,7 +60057,7 @@
       </c>
       <c r="S625" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T625" t="n">
@@ -60152,7 +60152,7 @@
       </c>
       <c r="S626" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T626" t="n">
@@ -60247,7 +60247,7 @@
       </c>
       <c r="S627" t="inlineStr">
         <is>
-          <t>19-08-2021 08:30</t>
+          <t>2021-08-19 08:30:00</t>
         </is>
       </c>
       <c r="T627" t="n">
@@ -60342,7 +60342,7 @@
       </c>
       <c r="S628" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T628" t="n">
@@ -60437,7 +60437,7 @@
       </c>
       <c r="S629" t="inlineStr">
         <is>
-          <t>26-10-2021 08:30</t>
+          <t>2021-10-26 08:30:00</t>
         </is>
       </c>
       <c r="T629" t="n">
@@ -60532,7 +60532,7 @@
       </c>
       <c r="S630" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T630" t="n">
@@ -60627,7 +60627,7 @@
       </c>
       <c r="S631" t="inlineStr">
         <is>
-          <t>20-12-2021 08:30</t>
+          <t>2021-12-20 08:30:00</t>
         </is>
       </c>
       <c r="T631" t="n">
@@ -60722,7 +60722,7 @@
       </c>
       <c r="S632" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T632" t="inlineStr"/>
@@ -60815,7 +60815,7 @@
       </c>
       <c r="S633" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T633" t="inlineStr"/>
@@ -60908,7 +60908,7 @@
       </c>
       <c r="S634" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T634" t="inlineStr"/>
@@ -61001,7 +61001,7 @@
       </c>
       <c r="S635" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T635" t="inlineStr"/>
@@ -61094,7 +61094,7 @@
       </c>
       <c r="S636" t="inlineStr">
         <is>
-          <t>18-02-2021 08:30</t>
+          <t>2021-02-18 08:30:00</t>
         </is>
       </c>
       <c r="T636" t="inlineStr"/>
@@ -61187,7 +61187,7 @@
       </c>
       <c r="S637" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T637" t="inlineStr"/>
@@ -61280,7 +61280,7 @@
       </c>
       <c r="S638" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T638" t="n">
@@ -61375,7 +61375,7 @@
       </c>
       <c r="S639" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T639" t="n">
@@ -61470,7 +61470,7 @@
       </c>
       <c r="S640" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T640" t="n">
@@ -61565,7 +61565,7 @@
       </c>
       <c r="S641" t="inlineStr">
         <is>
-          <t>23-04-2021 08:30</t>
+          <t>2021-04-23 08:30:00</t>
         </is>
       </c>
       <c r="T641" t="n">
@@ -61660,7 +61660,7 @@
       </c>
       <c r="S642" t="inlineStr">
         <is>
-          <t>27-07-2021 08:30</t>
+          <t>2021-07-27 08:30:00</t>
         </is>
       </c>
       <c r="T642" t="n">
@@ -61755,7 +61755,7 @@
       </c>
       <c r="S643" t="inlineStr">
         <is>
-          <t>17-08-2021 08:30</t>
+          <t>2021-08-17 08:30:00</t>
         </is>
       </c>
       <c r="T643" t="n">
@@ -61850,7 +61850,7 @@
       </c>
       <c r="S644" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T644" t="n">
@@ -61945,7 +61945,7 @@
       </c>
       <c r="S645" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T645" t="n">
@@ -62040,7 +62040,7 @@
       </c>
       <c r="S646" t="inlineStr">
         <is>
-          <t>30-11-2021 08:30</t>
+          <t>2021-11-30 08:30:00</t>
         </is>
       </c>
       <c r="T646" t="n">
@@ -62135,7 +62135,7 @@
       </c>
       <c r="S647" t="inlineStr">
         <is>
-          <t>29-12-2021 08:30</t>
+          <t>2021-12-29 08:30:00</t>
         </is>
       </c>
       <c r="T647" t="n">
@@ -62230,7 +62230,7 @@
       </c>
       <c r="S648" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T648" t="n">
@@ -62325,7 +62325,7 @@
       </c>
       <c r="S649" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T649" t="n">
@@ -62420,7 +62420,7 @@
       </c>
       <c r="S650" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T650" t="n">
@@ -62515,7 +62515,7 @@
       </c>
       <c r="S651" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T651" t="n">
@@ -62610,7 +62610,7 @@
       </c>
       <c r="S652" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T652" t="n">
@@ -62705,7 +62705,7 @@
       </c>
       <c r="S653" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T653" t="n">
@@ -62800,7 +62800,7 @@
       </c>
       <c r="S654" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T654" t="n">
@@ -62895,7 +62895,7 @@
       </c>
       <c r="S655" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T655" t="n">
@@ -62990,7 +62990,7 @@
       </c>
       <c r="S656" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T656" t="n">
@@ -63085,7 +63085,7 @@
       </c>
       <c r="S657" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T657" t="n">
@@ -63180,7 +63180,7 @@
       </c>
       <c r="S658" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T658" t="inlineStr"/>
@@ -63273,7 +63273,7 @@
       </c>
       <c r="S659" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T659" t="inlineStr"/>
@@ -63366,7 +63366,7 @@
       </c>
       <c r="S660" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T660" t="inlineStr"/>
@@ -63459,7 +63459,7 @@
       </c>
       <c r="S661" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T661" t="n">
@@ -63554,7 +63554,7 @@
       </c>
       <c r="S662" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T662" t="n">
@@ -63649,7 +63649,7 @@
       </c>
       <c r="S663" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T663" t="n">
@@ -63744,7 +63744,7 @@
       </c>
       <c r="S664" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T664" t="n">
@@ -63839,7 +63839,7 @@
       </c>
       <c r="S665" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T665" t="n">
@@ -63934,7 +63934,7 @@
       </c>
       <c r="S666" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T666" t="n">
@@ -64029,7 +64029,7 @@
       </c>
       <c r="S667" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T667" t="n">
@@ -64124,7 +64124,7 @@
       </c>
       <c r="S668" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T668" t="n">
@@ -64219,7 +64219,7 @@
       </c>
       <c r="S669" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T669" t="n">
@@ -64314,7 +64314,7 @@
       </c>
       <c r="S670" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T670" t="n">
@@ -64409,7 +64409,7 @@
       </c>
       <c r="S671" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T671" t="n">
@@ -64504,7 +64504,7 @@
       </c>
       <c r="S672" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T672" t="n">
@@ -64599,7 +64599,7 @@
       </c>
       <c r="S673" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T673" t="n">
@@ -64694,7 +64694,7 @@
       </c>
       <c r="S674" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T674" t="n">
@@ -64789,7 +64789,7 @@
       </c>
       <c r="S675" t="inlineStr">
         <is>
-          <t>26-07-2021 08:30</t>
+          <t>2021-07-26 08:30:00</t>
         </is>
       </c>
       <c r="T675" t="n">
@@ -64884,7 +64884,7 @@
       </c>
       <c r="S676" t="inlineStr">
         <is>
-          <t>20-08-2021 08:30</t>
+          <t>2021-08-20 08:30:00</t>
         </is>
       </c>
       <c r="T676" t="n">
@@ -64979,7 +64979,7 @@
       </c>
       <c r="S677" t="inlineStr">
         <is>
-          <t>20-09-2021 08:30</t>
+          <t>2021-09-20 08:30:00</t>
         </is>
       </c>
       <c r="T677" t="n">
@@ -65074,7 +65074,7 @@
       </c>
       <c r="S678" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T678" t="n">
@@ -65169,7 +65169,7 @@
       </c>
       <c r="S679" t="inlineStr">
         <is>
-          <t>29-11-2021 08:30</t>
+          <t>2021-11-29 08:30:00</t>
         </is>
       </c>
       <c r="T679" t="n">
@@ -65264,7 +65264,7 @@
       </c>
       <c r="S680" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T680" t="n">
@@ -65359,7 +65359,7 @@
       </c>
       <c r="S681" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T681" t="n">
@@ -65454,7 +65454,7 @@
       </c>
       <c r="S682" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T682" t="n">
@@ -65549,7 +65549,7 @@
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T683" t="n">
@@ -65644,7 +65644,7 @@
       </c>
       <c r="S684" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T684" t="n">
@@ -65739,7 +65739,7 @@
       </c>
       <c r="S685" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T685" t="n">
@@ -65834,7 +65834,7 @@
       </c>
       <c r="S686" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T686" t="n">
@@ -65929,7 +65929,7 @@
       </c>
       <c r="S687" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T687" t="n">
@@ -66024,7 +66024,7 @@
       </c>
       <c r="S688" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T688" t="n">
@@ -66119,7 +66119,7 @@
       </c>
       <c r="S689" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T689" t="n">
@@ -66214,7 +66214,7 @@
       </c>
       <c r="S690" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T690" t="n">
@@ -66309,7 +66309,7 @@
       </c>
       <c r="S691" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T691" t="n">
@@ -66404,7 +66404,7 @@
       </c>
       <c r="S692" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T692" t="n">
@@ -66499,7 +66499,7 @@
       </c>
       <c r="S693" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T693" t="n">
@@ -66594,7 +66594,7 @@
       </c>
       <c r="S694" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T694" t="n">
@@ -66689,7 +66689,7 @@
       </c>
       <c r="S695" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T695" t="n">
@@ -66784,7 +66784,7 @@
       </c>
       <c r="S696" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T696" t="n">
@@ -66879,7 +66879,7 @@
       </c>
       <c r="S697" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T697" t="n">
@@ -66974,7 +66974,7 @@
       </c>
       <c r="S698" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T698" t="n">
@@ -67069,7 +67069,7 @@
       </c>
       <c r="S699" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T699" t="n">
@@ -67164,7 +67164,7 @@
       </c>
       <c r="S700" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T700" t="n">
@@ -67259,7 +67259,7 @@
       </c>
       <c r="S701" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T701" t="n">
@@ -67354,7 +67354,7 @@
       </c>
       <c r="S702" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T702" t="inlineStr"/>
@@ -67447,7 +67447,7 @@
       </c>
       <c r="S703" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T703" t="inlineStr"/>
@@ -67540,7 +67540,7 @@
       </c>
       <c r="S704" t="inlineStr">
         <is>
-          <t>22-03-2021 08:30</t>
+          <t>2021-03-22 08:30:00</t>
         </is>
       </c>
       <c r="T704" t="inlineStr"/>
@@ -67633,7 +67633,7 @@
       </c>
       <c r="S705" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T705" t="n">
@@ -67728,7 +67728,7 @@
       </c>
       <c r="S706" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T706" t="n">
@@ -67823,7 +67823,7 @@
       </c>
       <c r="S707" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T707" t="n">
@@ -67918,7 +67918,7 @@
       </c>
       <c r="S708" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T708" t="n">
@@ -68013,7 +68013,7 @@
       </c>
       <c r="S709" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T709" t="n">
@@ -68108,7 +68108,7 @@
       </c>
       <c r="S710" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T710" t="n">
@@ -68203,7 +68203,7 @@
       </c>
       <c r="S711" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T711" t="n">
@@ -68298,7 +68298,7 @@
       </c>
       <c r="S712" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T712" t="n">
@@ -68393,7 +68393,7 @@
       </c>
       <c r="S713" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T713" t="n">
@@ -68488,7 +68488,7 @@
       </c>
       <c r="S714" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T714" t="n">
@@ -68583,7 +68583,7 @@
       </c>
       <c r="S715" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T715" t="inlineStr"/>
@@ -68676,7 +68676,7 @@
       </c>
       <c r="S716" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T716" t="inlineStr"/>
@@ -68769,7 +68769,7 @@
       </c>
       <c r="S717" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T717" t="inlineStr"/>
@@ -68862,7 +68862,7 @@
       </c>
       <c r="S718" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T718" t="n">
@@ -68957,7 +68957,7 @@
       </c>
       <c r="S719" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T719" t="n">
@@ -69052,7 +69052,7 @@
       </c>
       <c r="S720" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T720" t="n">
@@ -69147,7 +69147,7 @@
       </c>
       <c r="S721" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T721" t="n">
@@ -69242,7 +69242,7 @@
       </c>
       <c r="S722" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T722" t="n">
@@ -69337,7 +69337,7 @@
       </c>
       <c r="S723" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T723" t="n">
@@ -69432,7 +69432,7 @@
       </c>
       <c r="S724" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T724" t="n">
@@ -69527,7 +69527,7 @@
       </c>
       <c r="S725" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T725" t="n">
@@ -69622,7 +69622,7 @@
       </c>
       <c r="S726" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T726" t="n">
@@ -69717,7 +69717,7 @@
       </c>
       <c r="S727" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T727" t="n">
@@ -69812,7 +69812,7 @@
       </c>
       <c r="S728" t="inlineStr">
         <is>
-          <t>20-01-2021 08:30</t>
+          <t>2021-01-20 08:30:00</t>
         </is>
       </c>
       <c r="T728" t="inlineStr"/>
@@ -69905,7 +69905,7 @@
       </c>
       <c r="S729" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T729" t="inlineStr"/>
@@ -69998,7 +69998,7 @@
       </c>
       <c r="S730" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T730" t="inlineStr"/>
@@ -70091,7 +70091,7 @@
       </c>
       <c r="S731" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T731" t="n">
@@ -70186,7 +70186,7 @@
       </c>
       <c r="S732" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T732" t="n">
@@ -70281,7 +70281,7 @@
       </c>
       <c r="S733" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T733" t="n">
@@ -70376,7 +70376,7 @@
       </c>
       <c r="S734" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T734" t="n">
@@ -70471,7 +70471,7 @@
       </c>
       <c r="S735" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T735" t="n">
@@ -70566,7 +70566,7 @@
       </c>
       <c r="S736" t="inlineStr">
         <is>
-          <t>16-07-2021 08:30</t>
+          <t>2021-07-16 08:30:00</t>
         </is>
       </c>
       <c r="T736" t="n">
@@ -70661,7 +70661,7 @@
       </c>
       <c r="S737" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T737" t="n">
@@ -70756,7 +70756,7 @@
       </c>
       <c r="S738" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T738" t="n">
@@ -70851,7 +70851,7 @@
       </c>
       <c r="S739" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T739" t="n">
@@ -70946,7 +70946,7 @@
       </c>
       <c r="S740" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T740" t="n">
@@ -71041,7 +71041,7 @@
       </c>
       <c r="S741" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T741" t="inlineStr"/>
@@ -71134,7 +71134,7 @@
       </c>
       <c r="S742" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T742" t="inlineStr"/>
@@ -71227,7 +71227,7 @@
       </c>
       <c r="S743" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T743" t="inlineStr"/>
@@ -71320,7 +71320,7 @@
       </c>
       <c r="S744" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T744" t="n">
@@ -71415,7 +71415,7 @@
       </c>
       <c r="S745" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T745" t="n">
@@ -71510,7 +71510,7 @@
       </c>
       <c r="S746" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T746" t="n">
@@ -71605,7 +71605,7 @@
       </c>
       <c r="S747" t="inlineStr">
         <is>
-          <t>27-04-2021 08:30</t>
+          <t>2021-04-27 08:30:00</t>
         </is>
       </c>
       <c r="T747" t="n">
@@ -71700,7 +71700,7 @@
       </c>
       <c r="S748" t="inlineStr">
         <is>
-          <t>28-07-2021 08:30</t>
+          <t>2021-07-28 08:30:00</t>
         </is>
       </c>
       <c r="T748" t="n">
@@ -71795,7 +71795,7 @@
       </c>
       <c r="S749" t="inlineStr">
         <is>
-          <t>26-08-2021 08:30</t>
+          <t>2021-08-26 08:30:00</t>
         </is>
       </c>
       <c r="T749" t="n">
@@ -71890,7 +71890,7 @@
       </c>
       <c r="S750" t="inlineStr">
         <is>
-          <t>21-09-2021 08:30</t>
+          <t>2021-09-21 08:30:00</t>
         </is>
       </c>
       <c r="T750" t="n">
@@ -71985,7 +71985,7 @@
       </c>
       <c r="S751" t="inlineStr">
         <is>
-          <t>28-10-2021 08:30</t>
+          <t>2021-10-28 08:30:00</t>
         </is>
       </c>
       <c r="T751" t="n">
@@ -72080,7 +72080,7 @@
       </c>
       <c r="S752" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T752" t="n">
@@ -72175,7 +72175,7 @@
       </c>
       <c r="S753" t="inlineStr">
         <is>
-          <t>16-12-2021 08:30</t>
+          <t>2021-12-16 08:30:00</t>
         </is>
       </c>
       <c r="T753" t="n">
@@ -72270,7 +72270,7 @@
       </c>
       <c r="S754" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T754" t="n">
@@ -72365,7 +72365,7 @@
       </c>
       <c r="S755" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T755" t="n">
@@ -72460,7 +72460,7 @@
       </c>
       <c r="S756" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T756" t="n">
@@ -72555,7 +72555,7 @@
       </c>
       <c r="S757" t="inlineStr">
         <is>
-          <t>22-04-2021 08:30</t>
+          <t>2021-04-22 08:30:00</t>
         </is>
       </c>
       <c r="T757" t="n">
@@ -72650,7 +72650,7 @@
       </c>
       <c r="S758" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T758" t="n">
@@ -72745,7 +72745,7 @@
       </c>
       <c r="S759" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T759" t="n">
@@ -72840,7 +72840,7 @@
       </c>
       <c r="S760" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T760" t="n">
@@ -72935,7 +72935,7 @@
       </c>
       <c r="S761" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T761" t="n">
@@ -73030,7 +73030,7 @@
       </c>
       <c r="S762" t="inlineStr">
         <is>
-          <t>17-11-2021 08:30</t>
+          <t>2021-11-17 08:30:00</t>
         </is>
       </c>
       <c r="T762" t="n">
@@ -73125,7 +73125,7 @@
       </c>
       <c r="S763" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T763" t="n">
@@ -73220,7 +73220,7 @@
       </c>
       <c r="S764" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T764" t="inlineStr"/>
@@ -73313,7 +73313,7 @@
       </c>
       <c r="S765" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T765" t="inlineStr"/>
@@ -73406,7 +73406,7 @@
       </c>
       <c r="S766" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T766" t="inlineStr"/>
@@ -73499,7 +73499,7 @@
       </c>
       <c r="S767" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T767" t="n">
@@ -73594,7 +73594,7 @@
       </c>
       <c r="S768" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T768" t="n">
@@ -73689,7 +73689,7 @@
       </c>
       <c r="S769" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T769" t="n">
@@ -73784,7 +73784,7 @@
       </c>
       <c r="S770" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T770" t="n">
@@ -73879,7 +73879,7 @@
       </c>
       <c r="S771" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T771" t="n">
@@ -73974,7 +73974,7 @@
       </c>
       <c r="S772" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T772" t="n">
@@ -74069,7 +74069,7 @@
       </c>
       <c r="S773" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T773" t="n">
@@ -74164,7 +74164,7 @@
       </c>
       <c r="S774" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T774" t="n">
@@ -74259,7 +74259,7 @@
       </c>
       <c r="S775" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T775" t="n">
@@ -74354,7 +74354,7 @@
       </c>
       <c r="S776" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T776" t="n">
@@ -74449,7 +74449,7 @@
       </c>
       <c r="S777" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T777" t="n">
@@ -74544,7 +74544,7 @@
       </c>
       <c r="S778" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T778" t="inlineStr"/>
@@ -74637,7 +74637,7 @@
       </c>
       <c r="S779" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T779" t="inlineStr"/>
@@ -74730,7 +74730,7 @@
       </c>
       <c r="S780" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T780" t="inlineStr"/>
@@ -74823,7 +74823,7 @@
       </c>
       <c r="S781" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T781" t="inlineStr"/>
@@ -74916,7 +74916,7 @@
       </c>
       <c r="S782" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T782" t="inlineStr"/>
@@ -75009,7 +75009,7 @@
       </c>
       <c r="S783" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T783" t="inlineStr"/>
@@ -75102,7 +75102,7 @@
       </c>
       <c r="S784" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T784" t="n">
@@ -75197,7 +75197,7 @@
       </c>
       <c r="S785" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T785" t="n">
@@ -75292,7 +75292,7 @@
       </c>
       <c r="S786" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T786" t="n">
@@ -75387,7 +75387,7 @@
       </c>
       <c r="S787" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T787" t="n">
@@ -75482,7 +75482,7 @@
       </c>
       <c r="S788" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T788" t="n">
@@ -75577,7 +75577,7 @@
       </c>
       <c r="S789" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T789" t="n">
@@ -75672,7 +75672,7 @@
       </c>
       <c r="S790" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T790" t="n">
@@ -75767,7 +75767,7 @@
       </c>
       <c r="S791" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T791" t="n">
@@ -75862,7 +75862,7 @@
       </c>
       <c r="S792" t="inlineStr">
         <is>
-          <t>21-10-2021 08:30</t>
+          <t>2021-10-21 08:30:00</t>
         </is>
       </c>
       <c r="T792" t="n">
@@ -75957,7 +75957,7 @@
       </c>
       <c r="S793" t="inlineStr">
         <is>
-          <t>22-11-2021 08:30</t>
+          <t>2021-11-22 08:30:00</t>
         </is>
       </c>
       <c r="T793" t="n">
@@ -76052,7 +76052,7 @@
       </c>
       <c r="S794" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T794" t="n">
@@ -76147,7 +76147,7 @@
       </c>
       <c r="S795" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T795" t="inlineStr"/>
@@ -76240,7 +76240,7 @@
       </c>
       <c r="S796" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T796" t="inlineStr"/>
@@ -76333,7 +76333,7 @@
       </c>
       <c r="S797" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T797" t="inlineStr"/>
@@ -76426,7 +76426,7 @@
       </c>
       <c r="S798" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T798" t="inlineStr"/>
@@ -76519,7 +76519,7 @@
       </c>
       <c r="S799" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T799" t="inlineStr"/>
@@ -76612,7 +76612,7 @@
       </c>
       <c r="S800" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T800" t="inlineStr"/>
@@ -76705,7 +76705,7 @@
       </c>
       <c r="S801" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T801" t="inlineStr"/>
@@ -76798,7 +76798,7 @@
       </c>
       <c r="S802" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T802" t="inlineStr"/>
@@ -76891,7 +76891,7 @@
       </c>
       <c r="S803" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T803" t="inlineStr"/>
@@ -76984,7 +76984,7 @@
       </c>
       <c r="S804" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T804" t="inlineStr"/>
@@ -77077,7 +77077,7 @@
       </c>
       <c r="S805" t="inlineStr">
         <is>
-          <t>16-02-2021 08:30</t>
+          <t>2021-02-16 08:30:00</t>
         </is>
       </c>
       <c r="T805" t="inlineStr"/>
@@ -77170,7 +77170,7 @@
       </c>
       <c r="S806" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T806" t="inlineStr"/>
@@ -77263,7 +77263,7 @@
       </c>
       <c r="S807" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T807" t="n">
@@ -77364,7 +77364,7 @@
       </c>
       <c r="S808" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T808" t="n">
@@ -77465,7 +77465,7 @@
       </c>
       <c r="S809" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T809" t="n">
@@ -77566,7 +77566,7 @@
       </c>
       <c r="S810" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T810" t="n">
@@ -77667,7 +77667,7 @@
       </c>
       <c r="S811" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T811" t="n">
@@ -77768,7 +77768,7 @@
       </c>
       <c r="S812" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T812" t="n">
@@ -77869,7 +77869,7 @@
       </c>
       <c r="S813" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T813" t="inlineStr"/>
@@ -77962,7 +77962,7 @@
       </c>
       <c r="S814" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T814" t="inlineStr"/>
@@ -78055,7 +78055,7 @@
       </c>
       <c r="S815" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T815" t="inlineStr"/>
@@ -78148,7 +78148,7 @@
       </c>
       <c r="S816" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T816" t="inlineStr"/>
@@ -78241,7 +78241,7 @@
       </c>
       <c r="S817" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T817" t="inlineStr"/>
@@ -78334,7 +78334,7 @@
       </c>
       <c r="S818" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T818" t="inlineStr"/>
